--- a/artfynd/A 30394-2025 artfynd.xlsx
+++ b/artfynd/A 30394-2025 artfynd.xlsx
@@ -782,45 +782,50 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126356138</v>
+        <v>126355403</v>
       </c>
       <c r="B3" t="n">
-        <v>91295</v>
+        <v>57656</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5321</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Skarpåsen, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>601302</v>
+        <v>601176</v>
       </c>
       <c r="R3" t="n">
-        <v>6925806</v>
+        <v>6925840</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,6 +858,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,50 +889,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126355403</v>
+        <v>126356138</v>
       </c>
       <c r="B4" t="n">
-        <v>57656</v>
+        <v>91295</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>5321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Skarpåsen, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>601176</v>
+        <v>601302</v>
       </c>
       <c r="R4" t="n">
-        <v>6925840</v>
+        <v>6925806</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -955,11 +960,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1198,7 +1198,7 @@
         <v>126356384</v>
       </c>
       <c r="B7" t="n">
-        <v>105384</v>
+        <v>105387</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 30394-2025 artfynd.xlsx
+++ b/artfynd/A 30394-2025 artfynd.xlsx
@@ -782,50 +782,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126355403</v>
+        <v>126356138</v>
       </c>
       <c r="B3" t="n">
-        <v>57656</v>
+        <v>91295</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>5321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Skarpåsen, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>601176</v>
+        <v>601302</v>
       </c>
       <c r="R3" t="n">
-        <v>6925840</v>
+        <v>6925806</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,11 +853,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,45 +879,50 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126356138</v>
+        <v>126355403</v>
       </c>
       <c r="B4" t="n">
-        <v>91295</v>
+        <v>57656</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5321</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Skarpåsen, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>601302</v>
+        <v>601176</v>
       </c>
       <c r="R4" t="n">
-        <v>6925806</v>
+        <v>6925840</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,6 +955,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 30394-2025 artfynd.xlsx
+++ b/artfynd/A 30394-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126356828</v>
       </c>
       <c r="B2" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>126356138</v>
       </c>
       <c r="B3" t="n">
-        <v>91295</v>
+        <v>91298</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>126355403</v>
       </c>
       <c r="B4" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>126355877</v>
       </c>
       <c r="B5" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>126356875</v>
       </c>
       <c r="B6" t="n">
-        <v>57653</v>
+        <v>57654</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         <v>126356384</v>
       </c>
       <c r="B7" t="n">
-        <v>105387</v>
+        <v>105396</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>126356208</v>
       </c>
       <c r="B8" t="n">
-        <v>58025</v>
+        <v>58027</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>126356498</v>
       </c>
       <c r="B9" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>126356611</v>
       </c>
       <c r="B10" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 30394-2025 artfynd.xlsx
+++ b/artfynd/A 30394-2025 artfynd.xlsx
@@ -1096,7 +1096,7 @@
         <v>126356875</v>
       </c>
       <c r="B6" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 30394-2025 artfynd.xlsx
+++ b/artfynd/A 30394-2025 artfynd.xlsx
@@ -1096,7 +1096,7 @@
         <v>126356875</v>
       </c>
       <c r="B6" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 30394-2025 artfynd.xlsx
+++ b/artfynd/A 30394-2025 artfynd.xlsx
@@ -1096,7 +1096,7 @@
         <v>126356875</v>
       </c>
       <c r="B6" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 30394-2025 artfynd.xlsx
+++ b/artfynd/A 30394-2025 artfynd.xlsx
@@ -1096,7 +1096,7 @@
         <v>126356875</v>
       </c>
       <c r="B6" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 30394-2025 artfynd.xlsx
+++ b/artfynd/A 30394-2025 artfynd.xlsx
@@ -1096,7 +1096,7 @@
         <v>126356875</v>
       </c>
       <c r="B6" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 30394-2025 artfynd.xlsx
+++ b/artfynd/A 30394-2025 artfynd.xlsx
@@ -1096,7 +1096,7 @@
         <v>126356875</v>
       </c>
       <c r="B6" t="n">
-        <v>57670</v>
+        <v>57681</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 30394-2025 artfynd.xlsx
+++ b/artfynd/A 30394-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126356828</v>
       </c>
       <c r="B2" t="n">
-        <v>57657</v>
+        <v>57736</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>126355403</v>
       </c>
       <c r="B4" t="n">
-        <v>57657</v>
+        <v>57736</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>126355877</v>
       </c>
       <c r="B5" t="n">
-        <v>57657</v>
+        <v>57736</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>126356498</v>
       </c>
       <c r="B9" t="n">
-        <v>57657</v>
+        <v>57736</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>126356611</v>
       </c>
       <c r="B10" t="n">
-        <v>57657</v>
+        <v>57736</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 30394-2025 artfynd.xlsx
+++ b/artfynd/A 30394-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126356828</v>
       </c>
       <c r="B2" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>126355403</v>
       </c>
       <c r="B4" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>126355877</v>
       </c>
       <c r="B5" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>126356498</v>
       </c>
       <c r="B9" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>126356611</v>
       </c>
       <c r="B10" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 30394-2025 artfynd.xlsx
+++ b/artfynd/A 30394-2025 artfynd.xlsx
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126356828</v>
+        <v>126356138</v>
       </c>
       <c r="B2" t="n">
-        <v>57741</v>
+        <v>91966</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>5321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Skarpåsen, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>601132</v>
+        <v>601302</v>
       </c>
       <c r="R2" t="n">
-        <v>6925888</v>
+        <v>6925806</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126356138</v>
+        <v>126356875</v>
       </c>
       <c r="B3" t="n">
-        <v>91298</v>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,34 +783,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5321</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Skarpåsen, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>601302</v>
+        <v>601131</v>
       </c>
       <c r="R3" t="n">
-        <v>6925806</v>
+        <v>6925908</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,7 +877,7 @@
         <v>126355403</v>
       </c>
       <c r="B4" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -986,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126355877</v>
+        <v>126355812</v>
       </c>
       <c r="B5" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1061,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på tall.  Flertalet äldre spår men högt upp på stammen finns färska spår.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126356875</v>
+        <v>126356498</v>
       </c>
       <c r="B6" t="n">
-        <v>57681</v>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1104,16 +1099,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1124,7 +1119,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1133,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>601131</v>
+        <v>601156</v>
       </c>
       <c r="R6" t="n">
-        <v>6925908</v>
+        <v>6925892</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,6 +1164,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1195,45 +1195,50 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126356384</v>
+        <v>126356611</v>
       </c>
       <c r="B7" t="n">
-        <v>105396</v>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221144</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Skarpåsen, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>601234</v>
+        <v>601186</v>
       </c>
       <c r="R7" t="n">
-        <v>6925874</v>
+        <v>6925912</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1266,6 +1271,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1292,27 +1302,27 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126356208</v>
+        <v>126356828</v>
       </c>
       <c r="B8" t="n">
-        <v>58027</v>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1323,7 +1333,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1332,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>601314</v>
+        <v>601132</v>
       </c>
       <c r="R8" t="n">
-        <v>6925860</v>
+        <v>6925888</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1368,6 +1378,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1394,27 +1409,27 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126356498</v>
+        <v>126356208</v>
       </c>
       <c r="B9" t="n">
-        <v>57741</v>
+        <v>58327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1425,7 +1440,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1434,10 +1449,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>601156</v>
+        <v>601314</v>
       </c>
       <c r="R9" t="n">
-        <v>6925892</v>
+        <v>6925860</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1470,11 +1485,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1501,50 +1511,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126356611</v>
+        <v>126356384</v>
       </c>
       <c r="B10" t="n">
-        <v>57741</v>
+        <v>106244</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>221144</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Skarpåsen, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>601186</v>
+        <v>601234</v>
       </c>
       <c r="R10" t="n">
-        <v>6925912</v>
+        <v>6925874</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1577,11 +1582,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 30394-2025 artfynd.xlsx
+++ b/artfynd/A 30394-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126356138</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126356875</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126355403</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1085,6 +1105,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126355812</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1192,6 +1217,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126356498</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1299,6 +1329,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126356611</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1406,6 +1441,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126356828</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1508,6 +1548,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126356208</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1605,8 +1650,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126356384</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>